--- a/data/trans_orig/P79A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79A_R-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>836</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26096</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>311276</t>
+          <t>318009</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>310625</t>
+          <t>314619</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>284524</t>
+          <t>312617</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265335</t>
+          <t>298394</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>595799</t>
+          <t>630626</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>574981</t>
+          <t>619471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>600907</t>
+          <t>634069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27262</t>
+          <t>26414</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15988</t>
+          <t>15505</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50685</t>
+          <t>43116</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,22 +1103,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15013</t>
+          <t>15080</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>36096</t>
+          <t>35222</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22930</t>
+          <t>22038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56192</t>
+          <t>52735</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>491128</t>
+          <t>504233</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467705</t>
+          <t>487531</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502402</t>
+          <t>515142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>506135</t>
+          <t>537686</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499956</t>
+          <t>531414</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510270</t>
+          <t>541512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>997263</t>
+          <t>1041919</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>977167</t>
+          <t>1024406</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1010429</t>
+          <t>1055103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>17080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>18143</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26676</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>308365</t>
+          <t>307779</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300469</t>
+          <t>300209</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312635</t>
+          <t>312384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>339141</t>
+          <t>346452</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331517</t>
+          <t>339301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>343883</t>
+          <t>351176</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>647507</t>
+          <t>654232</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>638502</t>
+          <t>644710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654566</t>
+          <t>661074</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18858</t>
+          <t>38071</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28208</t>
+          <t>33467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24672</t>
+          <t>38314</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15150</t>
+          <t>25625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38985</t>
+          <t>58399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>302387</t>
+          <t>354349</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293699</t>
+          <t>335074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>307551</t>
+          <t>362932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>461216</t>
+          <t>402443</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>447510</t>
+          <t>388494</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>468633</t>
+          <t>410392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>763602</t>
+          <t>756793</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>749289</t>
+          <t>736708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>773124</t>
+          <t>769482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>539</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>178250</t>
+          <t>205126</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175894</t>
+          <t>202382</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>257392</t>
+          <t>227321</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>251263</t>
+          <t>221399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>435642</t>
+          <t>432446</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>431552</t>
+          <t>427698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437160</t>
+          <t>434187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>10299</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23036</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>264271</t>
+          <t>263779</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256974</t>
+          <t>256748</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267478</t>
+          <t>267504</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>248644</t>
+          <t>253451</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>241973</t>
+          <t>245915</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252750</t>
+          <t>257708</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>512914</t>
+          <t>517230</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>503656</t>
+          <t>508361</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>518182</t>
+          <t>523458</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>11663</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>20859</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17090</t>
+          <t>20701</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28342</t>
+          <t>32520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26824</t>
+          <t>32364</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14669</t>
+          <t>21464</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>614545</t>
+          <t>708024</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>607286</t>
+          <t>698828</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>619376</t>
+          <t>713457</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>832175</t>
+          <t>751356</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>820923</t>
+          <t>739537</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>843072</t>
+          <t>759182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1446720</t>
+          <t>1459380</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1432200</t>
+          <t>1446427</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1458875</t>
+          <t>1470280</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20157</t>
+          <t>21697</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14978</t>
+          <t>16538</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>33212</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>918441</t>
+          <t>786100</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>908563</t>
+          <t>776375</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>925675</t>
+          <t>791654</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>708855</t>
+          <t>821347</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>702753</t>
+          <t>814793</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>712880</t>
+          <t>826288</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1627297</t>
+          <t>1607447</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1616924</t>
+          <t>1596191</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1636315</t>
+          <t>1614924</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51781</t>
+          <t>66461</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>95956</t>
+          <t>111769</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>74199</t>
+          <t>84279</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54238</t>
+          <t>67586</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>95737</t>
+          <t>106853</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>145352</t>
+          <t>169641</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>115676</t>
+          <t>141286</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>180662</t>
+          <t>202044</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3388664</t>
+          <t>3447400</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3363861</t>
+          <t>3420993</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3408036</t>
+          <t>3466301</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3638081</t>
+          <t>3652675</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3616543</t>
+          <t>3630101</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3658042</t>
+          <t>3669368</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7026745</t>
+          <t>7100075</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6991435</t>
+          <t>7067672</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7056421</t>
+          <t>7128430</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
